--- a/data/trans_orig/Q4506_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2012 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55441</t>
+          <t>53894</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89946</t>
+          <t>89729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>259290</t>
+          <t>258005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>322091</t>
+          <t>321477</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>326731</t>
+          <t>327706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>403768</t>
+          <t>398345</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59692</t>
+          <t>58371</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93977</t>
+          <t>92693</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>126311</t>
+          <t>125150</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171376</t>
+          <t>172139</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>193370</t>
+          <t>196346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250843</t>
+          <t>253792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86505</t>
+          <t>88612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>125882</t>
+          <t>127316</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>156317</t>
+          <t>158526</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208070</t>
+          <t>207648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>255305</t>
+          <t>253559</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>319632</t>
+          <t>322735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63736</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99353</t>
+          <t>99451</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77597</t>
+          <t>77489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115304</t>
+          <t>114846</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151182</t>
+          <t>149018</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203683</t>
+          <t>200288</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>608609</t>
+          <t>610275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>671265</t>
+          <t>673167</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>586431</t>
+          <t>587040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>659948</t>
+          <t>657962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1212915</t>
+          <t>1216105</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1315269</t>
+          <t>1311652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,77%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>130955</t>
+          <t>128772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180957</t>
+          <t>181142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>286091</t>
+          <t>284051</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>351486</t>
+          <t>350943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>430789</t>
+          <t>432465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>510775</t>
+          <t>514311</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144930</t>
+          <t>144840</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>197666</t>
+          <t>199286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241117</t>
+          <t>241591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>304315</t>
+          <t>304768</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>401083</t>
+          <t>402914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>482950</t>
+          <t>480629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>268798</t>
+          <t>264213</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>335353</t>
+          <t>329506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,82 +1654,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>16,82%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>385482</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>349864</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>427883</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>19,96%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>24,42%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>682662</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>635570</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>731178</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>18,39%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>17,12%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>385482</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>348666</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>422417</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>22,0%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>19,9%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>24,1%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>682662</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>633574</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>730013</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>17,07%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>252753</t>
+          <t>253779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>316948</t>
+          <t>313579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139899</t>
+          <t>141010</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188336</t>
+          <t>190301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409217</t>
+          <t>408986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>489798</t>
+          <t>488648</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1007847</t>
+          <t>1005153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1098722</t>
+          <t>1096939</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>575658</t>
+          <t>570265</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>657678</t>
+          <t>654216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1605182</t>
+          <t>1603173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1733879</t>
+          <t>1728034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31180</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59680</t>
+          <t>57840</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>80511</t>
+          <t>82094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119293</t>
+          <t>118497</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121309</t>
+          <t>120470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165935</t>
+          <t>169202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55546</t>
+          <t>54772</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88926</t>
+          <t>90079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>84141</t>
+          <t>82547</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120743</t>
+          <t>119860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>148924</t>
+          <t>147133</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198574</t>
+          <t>198086</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92200</t>
+          <t>92290</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>131244</t>
+          <t>132767</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71133</t>
+          <t>71064</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106925</t>
+          <t>106172</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>173333</t>
+          <t>173541</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>227914</t>
+          <t>228675</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61386</t>
+          <t>60139</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93546</t>
+          <t>93175</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>35577</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62747</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>103474</t>
+          <t>105918</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145587</t>
+          <t>148775</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155939</t>
+          <t>156420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>199881</t>
+          <t>200783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>101264</t>
+          <t>102081</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142683</t>
+          <t>140514</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>270456</t>
+          <t>268865</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>328722</t>
+          <t>330982</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>236116</t>
+          <t>237053</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>301984</t>
+          <t>298980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>659999</t>
+          <t>661614</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>757849</t>
+          <t>760514</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>914216</t>
+          <t>914536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1028388</t>
+          <t>1036595</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>284447</t>
+          <t>283337</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>355773</t>
+          <t>355436</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475692</t>
+          <t>477960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>561581</t>
+          <t>561254</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>784567</t>
+          <t>781660</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>892876</t>
+          <t>895118</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>473119</t>
+          <t>474535</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>556201</t>
+          <t>562297</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>610535</t>
+          <t>608565</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>703216</t>
+          <t>700056</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1103962</t>
+          <t>1100232</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1237559</t>
+          <t>1231923</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>401513</t>
+          <t>403863</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>482525</t>
+          <t>485609</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>273786</t>
+          <t>272970</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>342367</t>
+          <t>340688</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>698766</t>
+          <t>695230</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>796192</t>
+          <t>804816</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1807760</t>
+          <t>1808725</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1933163</t>
+          <t>1932055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1306129</t>
+          <t>1302925</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1422814</t>
+          <t>1419534</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3141414</t>
+          <t>3143814</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3317242</t>
+          <t>3321380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 50 o mayor el pasado verano al aire libre en 2016 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29354</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53742</t>
+          <t>53136</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>133018</t>
+          <t>132260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>180009</t>
+          <t>179491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>171991</t>
+          <t>169692</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225354</t>
+          <t>226273</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70644</t>
+          <t>68988</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104294</t>
+          <t>103253</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>150927</t>
+          <t>152165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202051</t>
+          <t>202828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228935</t>
+          <t>230348</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>293367</t>
+          <t>291877</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56021</t>
+          <t>57962</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87085</t>
+          <t>89290</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126653</t>
+          <t>129164</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174207</t>
+          <t>179078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>193735</t>
+          <t>193416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249746</t>
+          <t>250840</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58292</t>
+          <t>60379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92144</t>
+          <t>92539</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60161</t>
+          <t>58963</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94295</t>
+          <t>93112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>126352</t>
+          <t>130668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175071</t>
+          <t>177559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>451405</t>
+          <t>453547</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>506141</t>
+          <t>504360</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>400585</t>
+          <t>399316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>467480</t>
+          <t>463658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>869371</t>
+          <t>866328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>957766</t>
+          <t>955379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,83%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174137</t>
+          <t>171836</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>230830</t>
+          <t>228717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>381000</t>
+          <t>377375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>450606</t>
+          <t>453778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>567136</t>
+          <t>566203</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>662143</t>
+          <t>655502</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>377491</t>
+          <t>372900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447209</t>
+          <t>446928</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>542352</t>
+          <t>551062</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>629337</t>
+          <t>630260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>947438</t>
+          <t>946282</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1058067</t>
+          <t>1057603</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,16%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>329213</t>
+          <t>327622</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>400285</t>
+          <t>398242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>334003</t>
+          <t>332079</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>403346</t>
+          <t>402565</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>675186</t>
+          <t>680508</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>780010</t>
+          <t>783038</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>233535</t>
+          <t>234311</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>295582</t>
+          <t>298424</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>153418</t>
+          <t>151590</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204344</t>
+          <t>202063</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>402405</t>
+          <t>402453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>480775</t>
+          <t>481379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>780729</t>
+          <t>778749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>870503</t>
+          <t>872601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>398055</t>
+          <t>398292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474499</t>
+          <t>474312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205240</t>
+          <t>1200831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1324447</t>
+          <t>1322063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75752</t>
+          <t>74912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>113571</t>
+          <t>111712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148463</t>
+          <t>146497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190735</t>
+          <t>189964</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232251</t>
+          <t>231946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>291406</t>
+          <t>290152</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125263</t>
+          <t>126516</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167109</t>
+          <t>167722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131048</t>
+          <t>131577</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>172993</t>
+          <t>171592</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268932</t>
+          <t>268585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>332598</t>
+          <t>329186</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82552</t>
+          <t>82607</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119753</t>
+          <t>121115</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89265</t>
+          <t>88882</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>126332</t>
+          <t>128357</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>179528</t>
+          <t>182337</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>232637</t>
+          <t>233410</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44100</t>
+          <t>46016</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72650</t>
+          <t>75432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>24064</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46470</t>
+          <t>46510</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74578</t>
+          <t>74542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110243</t>
+          <t>112157</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126427</t>
+          <t>125085</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>169430</t>
+          <t>167946</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71224</t>
+          <t>73260</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107158</t>
+          <t>107866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>209434</t>
+          <t>207040</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>264872</t>
+          <t>265439</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>298725</t>
+          <t>297121</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>367425</t>
+          <t>369528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>690074</t>
+          <t>686445</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>786323</t>
+          <t>780406</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1013591</t>
+          <t>1008136</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1132116</t>
+          <t>1136829</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>600582</t>
+          <t>598804</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>694011</t>
+          <t>689815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>861198</t>
+          <t>865052</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>969889</t>
+          <t>968432</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1489662</t>
+          <t>1493838</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1633560</t>
+          <t>1635981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>489892</t>
+          <t>488640</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>578540</t>
+          <t>577759</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>578698</t>
+          <t>581368</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>669525</t>
+          <t>671286</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1089490</t>
+          <t>1087179</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1219230</t>
+          <t>1220508</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>357366</t>
+          <t>358450</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>435991</t>
+          <t>433477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,12 +6090,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>254667</t>
+          <t>254251</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>322699</t>
+          <t>319669</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>634929</t>
+          <t>633589</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>734191</t>
+          <t>735577</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1396212</t>
+          <t>1398907</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1511916</t>
+          <t>1515046</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>903581</t>
+          <t>899034</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1015024</t>
+          <t>1012797</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2331987</t>
+          <t>2325830</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2490966</t>
+          <t>2489787</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4506_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4506_R-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53894</t>
+          <t>55288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89729</t>
+          <t>88742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>258005</t>
+          <t>259714</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>321477</t>
+          <t>321583</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>327706</t>
+          <t>324683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>398345</t>
+          <t>396749</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58371</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92693</t>
+          <t>92995</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>125150</t>
+          <t>125236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172139</t>
+          <t>170158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196346</t>
+          <t>194125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>253792</t>
+          <t>253154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88612</t>
+          <t>87808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>127316</t>
+          <t>128548</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158526</t>
+          <t>157378</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207648</t>
+          <t>208307</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>253559</t>
+          <t>257014</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>322735</t>
+          <t>321467</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>64980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99451</t>
+          <t>99882</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>77489</t>
+          <t>78478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114846</t>
+          <t>114270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>149018</t>
+          <t>149789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>200288</t>
+          <t>201935</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>610275</t>
+          <t>612746</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>673167</t>
+          <t>672527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>587040</t>
+          <t>584995</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>657962</t>
+          <t>660080</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1216105</t>
+          <t>1209238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1311652</t>
+          <t>1306539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>128772</t>
+          <t>131692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181142</t>
+          <t>181791</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>284051</t>
+          <t>283833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>350943</t>
+          <t>350505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>432465</t>
+          <t>431684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>514311</t>
+          <t>516854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144840</t>
+          <t>147584</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199286</t>
+          <t>200342</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>241591</t>
+          <t>241776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>304768</t>
+          <t>306080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>402914</t>
+          <t>402961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>480629</t>
+          <t>484265</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,05%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264213</t>
+          <t>266058</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>329506</t>
+          <t>331257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349864</t>
+          <t>350009</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>427883</t>
+          <t>422217</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>635570</t>
+          <t>639019</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>731178</t>
+          <t>732571</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>253779</t>
+          <t>252675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>313579</t>
+          <t>318720</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141010</t>
+          <t>138528</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190301</t>
+          <t>189080</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>408986</t>
+          <t>407140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>488648</t>
+          <t>487095</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1005153</t>
+          <t>1007977</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1096939</t>
+          <t>1101146</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>570265</t>
+          <t>578029</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>654216</t>
+          <t>657847</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1603173</t>
+          <t>1609492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1728034</t>
+          <t>1730353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,62%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57840</t>
+          <t>61566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82094</t>
+          <t>82059</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>118497</t>
+          <t>119054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120470</t>
+          <t>119132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169202</t>
+          <t>168694</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,01%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54772</t>
+          <t>54316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90079</t>
+          <t>89779</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>82547</t>
+          <t>82332</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119860</t>
+          <t>119600</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>147133</t>
+          <t>148969</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198086</t>
+          <t>199326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92290</t>
+          <t>94633</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132767</t>
+          <t>133139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71064</t>
+          <t>70155</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>106172</t>
+          <t>107141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>173541</t>
+          <t>169637</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228675</t>
+          <t>225571</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,08%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60139</t>
+          <t>59460</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93175</t>
+          <t>94582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35577</t>
+          <t>34963</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>61290</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>105918</t>
+          <t>104533</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148775</t>
+          <t>149600</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156420</t>
+          <t>156743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200783</t>
+          <t>202782</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102081</t>
+          <t>103116</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140514</t>
+          <t>142147</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>268865</t>
+          <t>271109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>330982</t>
+          <t>333436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>237053</t>
+          <t>235395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>298980</t>
+          <t>298729</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>661614</t>
+          <t>659464</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>760514</t>
+          <t>759806</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>914536</t>
+          <t>917885</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1036595</t>
+          <t>1038906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>283337</t>
+          <t>282578</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>355436</t>
+          <t>351824</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>477960</t>
+          <t>479079</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>561254</t>
+          <t>565683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>781660</t>
+          <t>773770</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>895118</t>
+          <t>893567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>474535</t>
+          <t>475368</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>562297</t>
+          <t>557878</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>608565</t>
+          <t>610562</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>700056</t>
+          <t>703365</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1100232</t>
+          <t>1109939</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1231923</t>
+          <t>1239496</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>403863</t>
+          <t>399537</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>485609</t>
+          <t>480285</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>272970</t>
+          <t>269723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>340688</t>
+          <t>340560</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>695230</t>
+          <t>697391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>804816</t>
+          <t>799321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1808725</t>
+          <t>1814245</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1932055</t>
+          <t>1935372</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1302925</t>
+          <t>1300562</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1419534</t>
+          <t>1417131</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3143814</t>
+          <t>3138534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3321380</t>
+          <t>3317593</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,67%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>53760</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>132260</t>
+          <t>131784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>179491</t>
+          <t>181628</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169692</t>
+          <t>170776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>226273</t>
+          <t>224457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68988</t>
+          <t>69427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103253</t>
+          <t>102359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152165</t>
+          <t>151804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202828</t>
+          <t>202894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>230348</t>
+          <t>230825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>291877</t>
+          <t>289704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57962</t>
+          <t>55238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89290</t>
+          <t>86966</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>129164</t>
+          <t>130629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179078</t>
+          <t>179747</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>193416</t>
+          <t>196149</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>250840</t>
+          <t>253379</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>59577</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92539</t>
+          <t>93938</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4044,12 +4044,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58963</t>
+          <t>60839</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93112</t>
+          <t>93890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130668</t>
+          <t>125505</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>177559</t>
+          <t>175709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>453547</t>
+          <t>453003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504360</t>
+          <t>506035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>399316</t>
+          <t>399239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>463658</t>
+          <t>471177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>866328</t>
+          <t>871639</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>955379</t>
+          <t>952226</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,65%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171836</t>
+          <t>170943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228717</t>
+          <t>226892</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>377375</t>
+          <t>379161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>453778</t>
+          <t>451783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>566203</t>
+          <t>566278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>655502</t>
+          <t>656775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>372900</t>
+          <t>375732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>446928</t>
+          <t>447246</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>551062</t>
+          <t>546830</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>630260</t>
+          <t>630487</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>946282</t>
+          <t>945734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1057603</t>
+          <t>1056242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>327622</t>
+          <t>328614</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>398242</t>
+          <t>395820</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>332079</t>
+          <t>327950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>402565</t>
+          <t>402410</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>680508</t>
+          <t>675705</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>783038</t>
+          <t>778794</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>234311</t>
+          <t>230743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>298424</t>
+          <t>295633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151590</t>
+          <t>153360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>202063</t>
+          <t>206247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>402453</t>
+          <t>398026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>481379</t>
+          <t>482530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>778749</t>
+          <t>785612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>872601</t>
+          <t>873902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>398292</t>
+          <t>399139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474312</t>
+          <t>471816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1200831</t>
+          <t>1196028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1322063</t>
+          <t>1315892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,55%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74912</t>
+          <t>77068</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>111712</t>
+          <t>113680</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>146497</t>
+          <t>145071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189964</t>
+          <t>190153</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231946</t>
+          <t>232794</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>290152</t>
+          <t>289804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126516</t>
+          <t>123831</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167722</t>
+          <t>167072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131577</t>
+          <t>131626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171592</t>
+          <t>174877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>268585</t>
+          <t>269436</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>329186</t>
+          <t>330760</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -5280,12 +5280,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82607</t>
+          <t>80675</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>121115</t>
+          <t>120327</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>88882</t>
+          <t>88968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>128357</t>
+          <t>127117</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>182337</t>
+          <t>180731</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>233410</t>
+          <t>232799</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -5393,12 +5393,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46016</t>
+          <t>43915</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75432</t>
+          <t>72857</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24064</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>46702</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74542</t>
+          <t>75089</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>112157</t>
+          <t>112156</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125085</t>
+          <t>126054</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>167946</t>
+          <t>168735</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73260</t>
+          <t>72402</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107866</t>
+          <t>108989</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>207040</t>
+          <t>206987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>265439</t>
+          <t>265630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -5736,12 +5736,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>297121</t>
+          <t>299281</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>369528</t>
+          <t>372418</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>686445</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>780406</t>
+          <t>787602</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1008136</t>
+          <t>1009324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1136829</t>
+          <t>1132986</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -5849,12 +5849,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598804</t>
+          <t>595410</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>689815</t>
+          <t>688624</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5864,12 +5864,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>865052</t>
+          <t>855334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>968432</t>
+          <t>963229</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1493838</t>
+          <t>1482360</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1635981</t>
+          <t>1631318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>488640</t>
+          <t>488419</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>577759</t>
+          <t>575773</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>581368</t>
+          <t>577907</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>671286</t>
+          <t>669596</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6012,12 +6012,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1087179</t>
+          <t>1096809</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1220508</t>
+          <t>1218498</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6075,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>358450</t>
+          <t>361371</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>433477</t>
+          <t>439136</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6090,82 +6090,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13,07%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>286350</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>255107</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>320085</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>683976</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>636051</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>734159</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>9,25%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>10,67%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>286350</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>254251</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>319669</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>683976</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>633589</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>735577</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>9,94%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1398907</t>
+          <t>1397430</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1515046</t>
+          <t>1514539</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>899034</t>
+          <t>900633</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1012797</t>
+          <t>1014531</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2325830</t>
+          <t>2335485</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2489787</t>
+          <t>2487183</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
